--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_o higgins.xlsx
@@ -63,12 +63,12 @@
     <t xml:space="preserve">Marchigüe</t>
   </si>
   <si>
+    <t xml:space="preserve">Pumanque</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pichidegua</t>
   </si>
   <si>
-    <t xml:space="preserve">Pumanque</t>
-  </si>
-  <si>
     <t xml:space="preserve">Quinta de Tilcoco</t>
   </si>
   <si>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:44</t>
+    <t xml:space="preserve">2026-09-09 22:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -721,7 +721,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>6113</v>
+        <v>6309</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2024</v>
@@ -738,7 +738,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>6309</v>
+        <v>6113</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2024</v>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:31</t>
+    <t xml:space="preserve">2026-09-12 19:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_o higgins.xlsx
@@ -63,12 +63,12 @@
     <t xml:space="preserve">Marchigüe</t>
   </si>
   <si>
+    <t xml:space="preserve">Pichidegua</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pumanque</t>
   </si>
   <si>
-    <t xml:space="preserve">Pichidegua</t>
-  </si>
-  <si>
     <t xml:space="preserve">Quinta de Tilcoco</t>
   </si>
   <si>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:47</t>
+    <t xml:space="preserve">2026-09-24 00:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -721,7 +721,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>6309</v>
+        <v>6113</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2024</v>
@@ -738,7 +738,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>6113</v>
+        <v>6309</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2024</v>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:25</t>
+    <t xml:space="preserve">2026-09-27 22:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:14</t>
+    <t xml:space="preserve">2026-10-01 20:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:54</t>
+    <t xml:space="preserve">2026-10-02 13:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:14</t>
+    <t xml:space="preserve">2026-10-04 08:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:10</t>
+    <t xml:space="preserve">2026-10-05 08:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
